--- a/tw-core/src/test/resources/dev.hertlein.timesheetwizard.core.exporting.domain.service.strategy/timesheet_v3_PiedPiper_20220101-20221231.xlsx
+++ b/tw-core/src/test/resources/dev.hertlein.timesheetwizard.core.exporting.domain.service.strategy/timesheet_v3_PiedPiper_20220101-20221231.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tino/IdeaProjects/timesheet-wizard/tw-core/src/test/resources/dev.hertlein.timesheetwizard.core.exporting.domain.service.strategy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AA4AC9-DAF4-0A43-8C66-CFFFA7F4A0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3EAAD6-4E46-7740-B4EF-31C6AAA121A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25520" yWindow="660" windowWidth="20260" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24580" yWindow="1540" windowWidth="20260" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projektzeit" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Mitarbeiter</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>a-description</t>
+  </si>
+  <si>
+    <t>a-tag</t>
   </si>
 </sst>
 </file>
@@ -584,6 +587,9 @@
       <c r="G2" t="s">
         <v>15</v>
       </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
       <c r="I2">
         <v>1</v>
       </c>
